--- a/data/trans_orig/IP22C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Clase-trans_orig.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>31511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35652</t>
+          <t>36063</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>40887</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>33354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37813</t>
+          <t>37811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40435</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>37012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42621</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74400</t>
+          <t>74744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82303</t>
+          <t>82267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32465</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23343</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>111326</t>
+          <t>110914</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130572</t>
+          <t>130595</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>139750</t>
+          <t>139778</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>245193</t>
+          <t>245056</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257097</t>
+          <t>257300</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41522</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26934</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32547</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49189</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55259</t>
+          <t>54924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62441</t>
+          <t>62484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107119</t>
+          <t>106970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116274</t>
+          <t>116217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42133</t>
+          <t>42130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63642</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70845</t>
+          <t>70357</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>136188</t>
+          <t>135524</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145032</t>
+          <t>144835</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>170642</t>
+          <t>170354</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182574</t>
+          <t>182041</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>309649</t>
+          <t>310238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>325055</t>
+          <t>325158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>26115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41364</t>
+          <t>41528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22831</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60651</t>
+          <t>61571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70306</t>
+          <t>70541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46585</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94832</t>
+          <t>94683</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104767</t>
+          <t>104937</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88030</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99765</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>187562</t>
+          <t>187175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>203131</t>
+          <t>202913</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24712</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>34402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31220</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>33997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>59680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69716</t>
+          <t>69892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83156</t>
+          <t>82714</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91890</t>
+          <t>91694</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92890</t>
+          <t>93722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104880</t>
+          <t>104876</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179511</t>
+          <t>180148</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>193952</t>
+          <t>194658</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
